--- a/AAII_Financials/Quarterly/ONON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ONON_QTR_FIN.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>ONON</t>
   </si>
@@ -669,227 +669,240 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1052400</v>
+      </c>
+      <c r="E8" s="3">
         <v>938000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>942100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>669400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>631800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>531000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>496500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>396600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>305500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>265300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>463300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>240800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>338300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>272800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>177400</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>364600</v>
+      </c>
+      <c r="E9" s="3">
         <v>338500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>362600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>253600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>253100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>210100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>164600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>137000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>127900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>188000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>95800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>137500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>127900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>687700</v>
+      </c>
+      <c r="E10" s="3">
         <v>599500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>579400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>415800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>378700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>320900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>295600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>232100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>168500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>137400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>275200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>145000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>144900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>99600</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,29 +920,30 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>13400</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>10600</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>10600</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,8 +1018,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1030,8 +1050,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1048,55 +1068,61 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
         <v>20700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>11100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1111,102 +1137,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>904800</v>
+      </c>
+      <c r="E17" s="3">
         <v>834500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>825500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>611500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>579100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>483100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>452600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>380800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>277800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>261500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>637200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>214400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>324900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>259700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>207800</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>147500</v>
+      </c>
+      <c r="E18" s="3">
         <v>103500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>116600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>52600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-173900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30400</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1224,243 +1257,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>25900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>178100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-34000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>106500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>54800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>46200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-33400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-19500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E21" s="3">
         <v>91300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-48200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>102400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>64200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-171100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E22" s="3">
         <v>-500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>-2100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>-1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>1600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>500</v>
       </c>
       <c r="Q22" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E23" s="3">
         <v>88300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-59500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>101100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-53300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-195700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31600</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-21600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-11200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1506,102 +1555,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E26" s="3">
         <v>87100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-51400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>98900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-197000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E27" s="3">
         <v>87100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-51400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>98900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-197000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,8 +1705,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1694,8 +1755,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,8 +1805,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,102 +1855,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-25900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-178100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>34000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-106500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-54800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-46200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>33400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>19500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E33" s="3">
         <v>87100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-51400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>98900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-197000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1929,107 +2005,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E35" s="3">
         <v>87100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-51400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>98900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-197000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2047,8 +2132,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2066,290 +2152,309 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1492100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1286200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1064500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1020000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>726000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>587400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>376700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>401200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>584000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>704800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>739500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>742500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E42" s="3">
         <v>45100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>21100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>20800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>41600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>34000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>589700</v>
+      </c>
+      <c r="E43" s="3">
         <v>479100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>496200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>329100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>389800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>274800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>336000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>241800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>197000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>146900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>142900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>116200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>114400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>585300</v>
+      </c>
+      <c r="E44" s="3">
         <v>529400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>453200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>462600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>446600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>423400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>487100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>427800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>227000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>182800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>151900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>160500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>157500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E45" s="3">
         <v>92600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>54100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>66100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2837900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2474800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2177700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1941900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1670900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1367200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1291400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1137200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1110300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1142300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1092300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1109100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>420300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2377,8 +2482,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2395,102 +2500,111 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>874000</v>
+      </c>
+      <c r="E48" s="3">
         <v>810800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>759200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>497500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>479400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>365300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>265100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>247400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>249900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>255500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>240400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>213600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>195400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E49" s="3">
         <v>68400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>68700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>76700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>75300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>76000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>59700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>64900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>65100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>62100</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2536,8 +2650,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2583,16 +2700,19 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
         <v>100</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2600,38 +2720,41 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>4300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2677,55 +2800,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4013500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3575800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3198400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2622800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2276700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1891800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1717700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1495000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1437100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1467000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1400200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1391100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>681600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2743,8 +2872,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2762,290 +2892,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E57" s="3">
         <v>195200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>202100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>183700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>164900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>77300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>48100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>52000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>80800</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E58" s="3">
         <v>102400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>89200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>46000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>26100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>62700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>21900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E59" s="3">
         <v>211200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>213000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>168200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>69300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>74700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>86900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>156700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>164700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>131700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>118400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1002500</v>
+      </c>
+      <c r="E60" s="3">
         <v>913600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>862500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>728800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>561000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>362900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>367800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>262500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>247200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>267500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>232100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>208900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>210900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>587400</v>
+      </c>
+      <c r="E61" s="3">
         <v>555300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>536800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>318400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>316500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>226000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>157500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>150100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>184700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>190300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>189400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>177600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>168200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E62" s="3">
         <v>29600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3091,8 +3240,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3138,8 +3290,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3185,55 +3340,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1647900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1517100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1441800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1086900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>906700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>615800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>570400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>446500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>457000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>478500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>439500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>400900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>393700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3251,8 +3412,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3298,8 +3460,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3345,8 +3510,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3392,8 +3560,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3439,55 +3610,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>814700</v>
+      </c>
+      <c r="E72" s="3">
         <v>561200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>322200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>256900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>119300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-63000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-118000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-113200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>980000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>106400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>956100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>104300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3533,8 +3710,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3580,8 +3760,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3627,55 +3810,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2365600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2058600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1756600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1535900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1369900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1276000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1147300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1048500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>980100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>988500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>960700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>990300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>288000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3721,107 +3910,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E81" s="3">
         <v>87100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-51400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>98900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-197000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34300</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3839,55 +4037,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E83" s="3">
         <v>12400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>22300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3933,8 +4135,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3980,8 +4185,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4027,8 +4235,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4074,8 +4285,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4121,55 +4335,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E89" s="3">
         <v>142600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>127300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>186300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>114100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>144200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-75600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-64600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-71100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-42200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4187,55 +4407,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4281,8 +4505,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4328,55 +4555,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4394,8 +4627,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4423,8 +4657,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4441,8 +4675,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4488,8 +4725,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4535,8 +4775,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4582,145 +4825,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>12600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>680300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>678600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>131900</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-38700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-16000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>17600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-16800</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>229300</v>
+      </c>
+      <c r="E102" s="3">
         <v>73300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>193400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>75700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>74300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-131900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-44700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>618900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>624700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>122500</v>
       </c>
     </row>
